--- a/data/trans_orig/P23_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97310</t>
+          <t>96316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131292</t>
+          <t>128414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>59384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87924</t>
+          <t>87449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164736</t>
+          <t>162977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209448</t>
+          <t>207146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141718</t>
+          <t>144596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175700</t>
+          <t>176694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172914</t>
+          <t>173389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203053</t>
+          <t>201454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>324400</t>
+          <t>326702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>369112</t>
+          <t>370871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170232</t>
+          <t>170777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215299</t>
+          <t>214858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101390</t>
+          <t>100114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138880</t>
+          <t>138589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280057</t>
+          <t>277674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>340943</t>
+          <t>339186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276734</t>
+          <t>277175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>321801</t>
+          <t>321256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365069</t>
+          <t>365360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>402559</t>
+          <t>403835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655039</t>
+          <t>656796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715925</t>
+          <t>718308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131192</t>
+          <t>127891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166810</t>
+          <t>165238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80097</t>
+          <t>78636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113030</t>
+          <t>111045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217039</t>
+          <t>217217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267638</t>
+          <t>268323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152036</t>
+          <t>153608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187654</t>
+          <t>190955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222382</t>
+          <t>224367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255315</t>
+          <t>256776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>386620</t>
+          <t>385935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437219</t>
+          <t>437041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,8%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152527</t>
+          <t>151701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190305</t>
+          <t>189434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88395</t>
+          <t>88224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122324</t>
+          <t>122388</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251443</t>
+          <t>249999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302825</t>
+          <t>301631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168366</t>
+          <t>169237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206144</t>
+          <t>206970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249132</t>
+          <t>249068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283061</t>
+          <t>283232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>478684</t>
+          <t>480128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68899</t>
+          <t>69990</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97989</t>
+          <t>98762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47563</t>
+          <t>47538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74107</t>
+          <t>74550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124773</t>
+          <t>124221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164600</t>
+          <t>162884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105319</t>
+          <t>104546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134409</t>
+          <t>133318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133561</t>
+          <t>133118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160105</t>
+          <t>160130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246376</t>
+          <t>248092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286203</t>
+          <t>286755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110384</t>
+          <t>109768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>143950</t>
+          <t>140783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>53205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79992</t>
+          <t>81218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>169337</t>
+          <t>170612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>212765</t>
+          <t>213940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126861</t>
+          <t>130028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160427</t>
+          <t>161043</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198152</t>
+          <t>196926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225629</t>
+          <t>224939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>336190</t>
+          <t>335015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>379618</t>
+          <t>378343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>211567</t>
+          <t>209558</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>258034</t>
+          <t>260404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139384</t>
+          <t>139565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181712</t>
+          <t>183821</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>364088</t>
+          <t>361195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>429141</t>
+          <t>430152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>356993</t>
+          <t>354623</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>403460</t>
+          <t>405469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>456507</t>
+          <t>454398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>498835</t>
+          <t>498654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>824105</t>
+          <t>823094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>889158</t>
+          <t>892051</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>291437</t>
+          <t>291198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>344170</t>
+          <t>343872</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>161761</t>
+          <t>164333</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>212613</t>
+          <t>211739</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>466065</t>
+          <t>465979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>540526</t>
+          <t>541106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>399625</t>
+          <t>399923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>452358</t>
+          <t>452597</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>570898</t>
+          <t>571772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>621750</t>
+          <t>619178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>986780</t>
+          <t>986200</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1061241</t>
+          <t>1061327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1325414</t>
+          <t>1329366</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1442511</t>
+          <t>1446641</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>814610</t>
+          <t>815961</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>918767</t>
+          <t>910974</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2170312</t>
+          <t>2166858</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2328069</t>
+          <t>2330261</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1832990</t>
+          <t>1828860</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1950087</t>
+          <t>1946135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2460430</t>
+          <t>2468223</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2564587</t>
+          <t>2563236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4326629</t>
+          <t>4324437</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4484386</t>
+          <t>4487840</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118851</t>
+          <t>117194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154504</t>
+          <t>153386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81742</t>
+          <t>81620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118134</t>
+          <t>115982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209983</t>
+          <t>208731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259882</t>
+          <t>259682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140234</t>
+          <t>141352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175887</t>
+          <t>177544</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>169111</t>
+          <t>171263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205503</t>
+          <t>205625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322101</t>
+          <t>322301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372000</t>
+          <t>373252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188150</t>
+          <t>183201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233188</t>
+          <t>232354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130167</t>
+          <t>131693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173579</t>
+          <t>174565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329260</t>
+          <t>328150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>395929</t>
+          <t>391029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272339</t>
+          <t>273173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317377</t>
+          <t>322326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350186</t>
+          <t>349200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>393598</t>
+          <t>392072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633363</t>
+          <t>638263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>700032</t>
+          <t>701142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109970</t>
+          <t>110828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>146552</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>72597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106431</t>
+          <t>105506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188874</t>
+          <t>190654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>238707</t>
+          <t>239508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179767</t>
+          <t>177494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214076</t>
+          <t>213218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233603</t>
+          <t>234528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>267701</t>
+          <t>267437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>425373</t>
+          <t>424572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475206</t>
+          <t>473426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>115229</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151987</t>
+          <t>154895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87304</t>
+          <t>87587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123086</t>
+          <t>123202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212110</t>
+          <t>212276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264525</t>
+          <t>265359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>221995</t>
+          <t>219087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261768</t>
+          <t>258753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265865</t>
+          <t>265749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301647</t>
+          <t>301364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>498408</t>
+          <t>497574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>550823</t>
+          <t>550657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77011</t>
+          <t>75999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107723</t>
+          <t>105888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52121</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80921</t>
+          <t>79231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138651</t>
+          <t>136593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>180083</t>
+          <t>176248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104895</t>
+          <t>106730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135607</t>
+          <t>136619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138670</t>
+          <t>140360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167470</t>
+          <t>167356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252126</t>
+          <t>255961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>293558</t>
+          <t>295616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100978</t>
+          <t>99270</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82745</t>
+          <t>82596</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130824</t>
+          <t>129850</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170817</t>
+          <t>172449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173003</t>
+          <t>174711</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205000</t>
+          <t>205801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197286</t>
+          <t>197435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226143</t>
+          <t>225885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>383195</t>
+          <t>381563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>423188</t>
+          <t>424162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>253972</t>
+          <t>252360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>306263</t>
+          <t>306468</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171643</t>
+          <t>171515</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222521</t>
+          <t>219930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>439566</t>
+          <t>439278</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>513292</t>
+          <t>509504</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>356525</t>
+          <t>356320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>408816</t>
+          <t>410428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>471332</t>
+          <t>473923</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>522210</t>
+          <t>522338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>843349</t>
+          <t>847137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>917075</t>
+          <t>917363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>269138</t>
+          <t>270123</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>324280</t>
+          <t>325363</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185211</t>
+          <t>187555</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>236367</t>
+          <t>237238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>469305</t>
+          <t>464760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>544732</t>
+          <t>542350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>453789</t>
+          <t>452706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>508931</t>
+          <t>507946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>586490</t>
+          <t>585619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>637646</t>
+          <t>635302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1056194</t>
+          <t>1058576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1131621</t>
+          <t>1136166</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1296941</t>
+          <t>1297780</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1415781</t>
+          <t>1415261</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>920492</t>
+          <t>921956</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1029014</t>
+          <t>1029669</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2245409</t>
+          <t>2252453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2417827</t>
+          <t>2413925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2009968</t>
+          <t>2010488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2128808</t>
+          <t>2127969</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2527313</t>
+          <t>2526658</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2635835</t>
+          <t>2634371</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4564249</t>
+          <t>4568151</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4736667</t>
+          <t>4729623</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89188</t>
+          <t>91451</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124119</t>
+          <t>125764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>60767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91416</t>
+          <t>88898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159955</t>
+          <t>160529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>206723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169642</t>
+          <t>167997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204573</t>
+          <t>202310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197287</t>
+          <t>199805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227839</t>
+          <t>227936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378776</t>
+          <t>375741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422509</t>
+          <t>421935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188202</t>
+          <t>184401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234075</t>
+          <t>231193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>121605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165004</t>
+          <t>164370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>321679</t>
+          <t>322146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>386255</t>
+          <t>382549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>267636</t>
+          <t>270518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313509</t>
+          <t>317310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355882</t>
+          <t>356516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>399582</t>
+          <t>399281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>636342</t>
+          <t>640048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>700918</t>
+          <t>700451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80584</t>
+          <t>81827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111956</t>
+          <t>113817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67302</t>
+          <t>66983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98919</t>
+          <t>98032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155752</t>
+          <t>157093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199656</t>
+          <t>201232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206609</t>
+          <t>204748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237981</t>
+          <t>236738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237390</t>
+          <t>238277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269007</t>
+          <t>269326</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>455218</t>
+          <t>453642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>499122</t>
+          <t>497781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124411</t>
+          <t>124447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162451</t>
+          <t>162638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>91976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128282</t>
+          <t>127693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224958</t>
+          <t>223284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>278803</t>
+          <t>277806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207513</t>
+          <t>207326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245553</t>
+          <t>245517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257716</t>
+          <t>258305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295930</t>
+          <t>294022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>477159</t>
+          <t>478156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>531004</t>
+          <t>532678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72236</t>
+          <t>70823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101956</t>
+          <t>99066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>69422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>123482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163283</t>
+          <t>163188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109265</t>
+          <t>112155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138985</t>
+          <t>140398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>149165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173542</t>
+          <t>173711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>266525</t>
+          <t>266620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305059</t>
+          <t>306326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74686</t>
+          <t>74857</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105899</t>
+          <t>105798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58397</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>89195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141938</t>
+          <t>143222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183393</t>
+          <t>182708</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157224</t>
+          <t>157325</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188437</t>
+          <t>188266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186017</t>
+          <t>183920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214718</t>
+          <t>214013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>352845</t>
+          <t>353530</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394300</t>
+          <t>393016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177639</t>
+          <t>177437</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225740</t>
+          <t>227392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151378</t>
+          <t>152448</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199805</t>
+          <t>199947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>342875</t>
+          <t>344381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>412632</t>
+          <t>411298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>429746</t>
+          <t>428094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>477847</t>
+          <t>478049</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>489534</t>
+          <t>489392</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>537961</t>
+          <t>536891</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>932193</t>
+          <t>933527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1001950</t>
+          <t>1000444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229606</t>
+          <t>228677</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>285832</t>
+          <t>284051</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>189432</t>
+          <t>189123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241509</t>
+          <t>239010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>436427</t>
+          <t>432061</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>511861</t>
+          <t>506546</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>492751</t>
+          <t>494532</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>548977</t>
+          <t>549906</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>584658</t>
+          <t>587157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636735</t>
+          <t>637044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1092889</t>
+          <t>1098204</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1168323</t>
+          <t>1172689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1133536</t>
+          <t>1132509</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1249039</t>
+          <t>1247052</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>873361</t>
+          <t>871670</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>978159</t>
+          <t>977404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2029989</t>
+          <t>2032585</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2191972</t>
+          <t>2190225</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2143375</t>
+          <t>2145362</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2258878</t>
+          <t>2259905</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2560944</t>
+          <t>2561699</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2665742</t>
+          <t>2667433</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4739545</t>
+          <t>4741292</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4901528</t>
+          <t>4898932</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96316</t>
+          <t>95803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128414</t>
+          <t>129604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59384</t>
+          <t>58146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87449</t>
+          <t>89529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162977</t>
+          <t>165016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207146</t>
+          <t>208363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144596</t>
+          <t>143406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176694</t>
+          <t>177207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173389</t>
+          <t>171309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201454</t>
+          <t>202692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>326702</t>
+          <t>325485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>370871</t>
+          <t>368832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170777</t>
+          <t>169113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214858</t>
+          <t>214860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100114</t>
+          <t>101059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138589</t>
+          <t>138707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277674</t>
+          <t>282604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>339186</t>
+          <t>342018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277175</t>
+          <t>277173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>321256</t>
+          <t>322920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365360</t>
+          <t>365242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403835</t>
+          <t>402890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656796</t>
+          <t>653964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718308</t>
+          <t>713378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127891</t>
+          <t>129821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165238</t>
+          <t>165614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78636</t>
+          <t>78956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111045</t>
+          <t>111715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217217</t>
+          <t>219016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268323</t>
+          <t>267746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153608</t>
+          <t>153232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>190955</t>
+          <t>189025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224367</t>
+          <t>223697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256776</t>
+          <t>256456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>385935</t>
+          <t>386512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437041</t>
+          <t>435242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151701</t>
+          <t>151497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189434</t>
+          <t>189144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88224</t>
+          <t>88874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122388</t>
+          <t>120804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249999</t>
+          <t>251219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301631</t>
+          <t>301471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169237</t>
+          <t>169527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206970</t>
+          <t>207174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249068</t>
+          <t>250652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283232</t>
+          <t>282582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428496</t>
+          <t>428656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>480128</t>
+          <t>478908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69990</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98762</t>
+          <t>98771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47538</t>
+          <t>46917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74550</t>
+          <t>74864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124221</t>
+          <t>122544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162884</t>
+          <t>163694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104546</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133318</t>
+          <t>132235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133118</t>
+          <t>132804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160130</t>
+          <t>160751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248092</t>
+          <t>247282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286755</t>
+          <t>288432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109768</t>
+          <t>110581</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140783</t>
+          <t>141426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53205</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81218</t>
+          <t>79207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170612</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>213940</t>
+          <t>211841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130028</t>
+          <t>129385</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161043</t>
+          <t>160230</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>196926</t>
+          <t>198937</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>225938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>335015</t>
+          <t>337114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>378343</t>
+          <t>378852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209558</t>
+          <t>210432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>260404</t>
+          <t>259116</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139565</t>
+          <t>139459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183821</t>
+          <t>184869</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>361195</t>
+          <t>364547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>430152</t>
+          <t>429546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>354623</t>
+          <t>355911</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>405469</t>
+          <t>404595</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>454398</t>
+          <t>453350</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>498654</t>
+          <t>498760</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>823094</t>
+          <t>823700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>892051</t>
+          <t>888699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>291198</t>
+          <t>291646</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>343872</t>
+          <t>345328</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164333</t>
+          <t>163321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211739</t>
+          <t>210281</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>465979</t>
+          <t>464724</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>541106</t>
+          <t>539888</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>399923</t>
+          <t>398467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>452597</t>
+          <t>452149</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>571772</t>
+          <t>573230</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>619178</t>
+          <t>620190</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>986200</t>
+          <t>987418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1061327</t>
+          <t>1062582</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1329366</t>
+          <t>1331274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1446641</t>
+          <t>1442553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>815961</t>
+          <t>815438</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>910974</t>
+          <t>919173</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2166858</t>
+          <t>2173732</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2330261</t>
+          <t>2325182</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1828860</t>
+          <t>1832948</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1946135</t>
+          <t>1944227</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2468223</t>
+          <t>2460024</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2563236</t>
+          <t>2563759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4324437</t>
+          <t>4329516</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4487840</t>
+          <t>4480966</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117194</t>
+          <t>119166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153386</t>
+          <t>153841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81620</t>
+          <t>81262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115982</t>
+          <t>115655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208731</t>
+          <t>210863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259682</t>
+          <t>259941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141352</t>
+          <t>140897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177544</t>
+          <t>175572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171263</t>
+          <t>171590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205625</t>
+          <t>205983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322301</t>
+          <t>322042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>373252</t>
+          <t>371120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183201</t>
+          <t>187620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232354</t>
+          <t>235397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131693</t>
+          <t>130178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174565</t>
+          <t>172547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>328150</t>
+          <t>321109</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391029</t>
+          <t>388223</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273173</t>
+          <t>270130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322326</t>
+          <t>317907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349200</t>
+          <t>351218</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>392072</t>
+          <t>393587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>638263</t>
+          <t>641069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>701142</t>
+          <t>708183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110828</t>
+          <t>108866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146552</t>
+          <t>144140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72597</t>
+          <t>69916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105506</t>
+          <t>103495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>190654</t>
+          <t>189268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239508</t>
+          <t>240164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177494</t>
+          <t>179906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>213218</t>
+          <t>215180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234528</t>
+          <t>236539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>267437</t>
+          <t>270118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>424572</t>
+          <t>423916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473426</t>
+          <t>474812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115229</t>
+          <t>112846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154895</t>
+          <t>149861</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87587</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123202</t>
+          <t>125371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212276</t>
+          <t>212272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265359</t>
+          <t>262530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>219087</t>
+          <t>224121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258753</t>
+          <t>261136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>263580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301364</t>
+          <t>300844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497574</t>
+          <t>500403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>550657</t>
+          <t>550661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75999</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105888</t>
+          <t>107896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>52304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79231</t>
+          <t>79572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>136775</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176248</t>
+          <t>179139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106730</t>
+          <t>104722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136619</t>
+          <t>137015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140360</t>
+          <t>140019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167356</t>
+          <t>167287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255961</t>
+          <t>253070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295616</t>
+          <t>295434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68180</t>
+          <t>68257</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99270</t>
+          <t>99518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>53824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>80585</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129850</t>
+          <t>129219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172449</t>
+          <t>171874</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174711</t>
+          <t>174463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205801</t>
+          <t>205724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197435</t>
+          <t>199446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225885</t>
+          <t>226207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>381563</t>
+          <t>382138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>424162</t>
+          <t>424793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>252360</t>
+          <t>254661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>306468</t>
+          <t>309869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171515</t>
+          <t>171807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219930</t>
+          <t>219680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>439278</t>
+          <t>439340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>509504</t>
+          <t>511071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>356320</t>
+          <t>352919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>410428</t>
+          <t>408127</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>473923</t>
+          <t>474173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>522338</t>
+          <t>522046</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>847137</t>
+          <t>845570</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>917363</t>
+          <t>917301</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>270123</t>
+          <t>269361</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>325363</t>
+          <t>323817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187555</t>
+          <t>181858</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>237238</t>
+          <t>236942</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>464760</t>
+          <t>468297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>542350</t>
+          <t>546756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>452706</t>
+          <t>454252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>507946</t>
+          <t>508708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>585619</t>
+          <t>585915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635302</t>
+          <t>640999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1058576</t>
+          <t>1054170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1136166</t>
+          <t>1132629</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1297780</t>
+          <t>1296778</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1415261</t>
+          <t>1414730</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>921956</t>
+          <t>920335</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1029669</t>
+          <t>1033648</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2252453</t>
+          <t>2253291</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2413925</t>
+          <t>2411864</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2010488</t>
+          <t>2011019</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2127969</t>
+          <t>2128971</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2526658</t>
+          <t>2522679</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2634371</t>
+          <t>2635992</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4568151</t>
+          <t>4570212</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4729623</t>
+          <t>4728785</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91451</t>
+          <t>92616</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125764</t>
+          <t>128033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60767</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88898</t>
+          <t>89324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160529</t>
+          <t>160117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206723</t>
+          <t>205814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167997</t>
+          <t>165728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202310</t>
+          <t>201145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199805</t>
+          <t>199379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227936</t>
+          <t>229382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>375741</t>
+          <t>376650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>421935</t>
+          <t>422347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184401</t>
+          <t>188244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231193</t>
+          <t>232741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121605</t>
+          <t>122407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164370</t>
+          <t>161765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>322146</t>
+          <t>320755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382549</t>
+          <t>382720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>270518</t>
+          <t>268970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317310</t>
+          <t>313467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356516</t>
+          <t>359121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>399281</t>
+          <t>398479</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>640048</t>
+          <t>639877</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>700451</t>
+          <t>701842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,63%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81827</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113817</t>
+          <t>111823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>66327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>98166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>155501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201232</t>
+          <t>200650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204748</t>
+          <t>206742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>236738</t>
+          <t>237791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238277</t>
+          <t>238143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269326</t>
+          <t>269982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>453642</t>
+          <t>454224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>497781</t>
+          <t>499373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124447</t>
+          <t>123898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162638</t>
+          <t>160522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91976</t>
+          <t>91997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127693</t>
+          <t>128018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223284</t>
+          <t>223929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277806</t>
+          <t>276410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207326</t>
+          <t>209442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245517</t>
+          <t>246066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258305</t>
+          <t>257980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294022</t>
+          <t>294001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>478156</t>
+          <t>479552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>532678</t>
+          <t>532033</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70823</t>
+          <t>72004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99066</t>
+          <t>99513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69422</t>
+          <t>70083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123482</t>
+          <t>124515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163188</t>
+          <t>161620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112155</t>
+          <t>111708</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140398</t>
+          <t>139217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149165</t>
+          <t>148504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173711</t>
+          <t>172558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>266620</t>
+          <t>268188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306326</t>
+          <t>305293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74857</t>
+          <t>73296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105798</t>
+          <t>103939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89195</t>
+          <t>88668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143222</t>
+          <t>141198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182708</t>
+          <t>185141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157325</t>
+          <t>159184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188266</t>
+          <t>189827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183920</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214013</t>
+          <t>214474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>353530</t>
+          <t>351097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>393016</t>
+          <t>395040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177437</t>
+          <t>177233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>227392</t>
+          <t>226674</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152448</t>
+          <t>153817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199947</t>
+          <t>198482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>344381</t>
+          <t>343365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>411298</t>
+          <t>413687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>428094</t>
+          <t>428812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>478049</t>
+          <t>478253</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>489392</t>
+          <t>490857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>536891</t>
+          <t>535522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>933527</t>
+          <t>931138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1000444</t>
+          <t>1001460</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>228677</t>
+          <t>229891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>284051</t>
+          <t>285416</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>189123</t>
+          <t>189186</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>239010</t>
+          <t>243262</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>432061</t>
+          <t>434405</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>506546</t>
+          <t>511045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>494532</t>
+          <t>493167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>549906</t>
+          <t>548692</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>587157</t>
+          <t>582905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>637044</t>
+          <t>636981</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1098204</t>
+          <t>1093705</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1172689</t>
+          <t>1170345</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,93%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1132509</t>
+          <t>1141425</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1247052</t>
+          <t>1252088</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>871670</t>
+          <t>871656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>984620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2032585</t>
+          <t>2034452</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2190225</t>
+          <t>2193205</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2145362</t>
+          <t>2140326</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2259905</t>
+          <t>2250989</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2561699</t>
+          <t>2554483</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2667433</t>
+          <t>2667447</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4741292</t>
+          <t>4738312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4898932</t>
+          <t>4897065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
